--- a/caseload-tracker/Import_Helper.xlsx
+++ b/caseload-tracker/Import_Helper.xlsx
@@ -630,7 +630,7 @@
     <row r="14">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Block 2: on 'Converted' select L6:AC405 (Booking date to Last updated by), Ctrl+C. In the tracker's Caseload tab click L5, then Home &gt; Paste &gt; Paste Values (the clipboard icon with 123). Or right-click &gt; Paste Options &gt; Values.</t>
+          <t>Block 2: on 'Converted' select L6:AA405 (Booking date to Last updated by), Ctrl+C. In the tracker's Caseload tab click L5, then Home &gt; Paste &gt; Paste Values (the clipboard icon with 123). Or right-click &gt; Paste Options &gt; Values.</t>
         </is>
       </c>
     </row>
@@ -665,7 +665,7 @@
     <row r="19">
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>• Fill in the new columns (GTT, Anti-D, IOL, BP, Bloods, Last updated by). The old info column goes into Risks. as you go.</t>
+          <t>• Fill in the new columns (GTT, Anti-D, IOL, BP, Last updated by) as you go. The old info column goes into Risks.</t>
         </is>
       </c>
     </row>
@@ -707,7 +707,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD405"/>
+  <dimension ref="A1:AB405"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -735,11 +735,9 @@
     <col width="12" customWidth="1" min="23" max="23"/>
     <col width="12" customWidth="1" min="24" max="24"/>
     <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="28" customWidth="1" min="26" max="26"/>
-    <col width="12" customWidth="1" min="27" max="27"/>
-    <col width="40" customWidth="1" min="28" max="28"/>
-    <col width="15" customWidth="1" min="29" max="29"/>
-    <col width="12" customWidth="1" min="30" max="30"/>
+    <col width="40" customWidth="1" min="26" max="26"/>
+    <col width="15" customWidth="1" min="27" max="27"/>
+    <col width="12" customWidth="1" min="28" max="28"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,17 +876,7 @@
           <t>BLOCK 2</t>
         </is>
       </c>
-      <c r="AB1" s="6" t="inlineStr">
-        <is>
-          <t>BLOCK 2</t>
-        </is>
-      </c>
-      <c r="AC1" s="6" t="inlineStr">
-        <is>
-          <t>BLOCK 2</t>
-        </is>
-      </c>
-      <c r="AD1" s="5" t="inlineStr">
+      <c r="AB1" s="5" t="inlineStr">
         <is>
           <t>calculated: skip</t>
         </is>
@@ -1022,25 +1010,15 @@
       </c>
       <c r="Z2" s="7" t="inlineStr">
         <is>
-          <t>Bloods needed</t>
-        </is>
-      </c>
-      <c r="AA2" s="7" t="inlineStr">
-        <is>
-          <t>Bloods date</t>
-        </is>
-      </c>
-      <c r="AB2" s="7" t="inlineStr">
-        <is>
           <t>Risks</t>
         </is>
       </c>
-      <c r="AC2" s="7" t="inlineStr">
+      <c r="AA2" s="7" t="inlineStr">
         <is>
           <t>Last updated by</t>
         </is>
       </c>
-      <c r="AD2" s="7" t="inlineStr">
+      <c r="AB2" s="7" t="inlineStr">
         <is>
           <t>Overdue</t>
         </is>
@@ -1132,15 +1110,13 @@
       <c r="W3" s="8" t="inlineStr"/>
       <c r="X3" s="8" t="inlineStr"/>
       <c r="Y3" s="8" t="inlineStr"/>
-      <c r="Z3" s="8" t="inlineStr"/>
-      <c r="AA3" s="8" t="inlineStr"/>
-      <c r="AB3" s="8" t="inlineStr">
+      <c r="Z3" s="8" t="inlineStr">
         <is>
           <t>info</t>
         </is>
       </c>
-      <c r="AC3" s="8" t="inlineStr"/>
-      <c r="AD3" s="9" t="n"/>
+      <c r="AA3" s="8" t="inlineStr"/>
+      <c r="AB3" s="9" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="10">
@@ -1239,15 +1215,7 @@
         <f>IF(AA3="","(new column)",IF(ISNUMBER(AA5),INDEX('Paste old sheet'!$A$1:$BZ$1,AA5),"NOT FOUND"))</f>
         <v/>
       </c>
-      <c r="AB4" s="10">
-        <f>IF(AB3="","(new column)",IF(ISNUMBER(AB5),INDEX('Paste old sheet'!$A$1:$BZ$1,AB5),"NOT FOUND"))</f>
-        <v/>
-      </c>
-      <c r="AC4" s="10">
-        <f>IF(AC3="","(new column)",IF(ISNUMBER(AC5),INDEX('Paste old sheet'!$A$1:$BZ$1,AC5),"NOT FOUND"))</f>
-        <v/>
-      </c>
-      <c r="AD4" s="9" t="n"/>
+      <c r="AB4" s="9" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="11">
@@ -1346,15 +1314,7 @@
         <f>IF(AA3="","",IFERROR(MATCH(AA3&amp;"*",'Paste old sheet'!$A$1:$BZ$1,0),""))</f>
         <v/>
       </c>
-      <c r="AB5" s="11">
-        <f>IF(AB3="","",IFERROR(MATCH(AB3&amp;"*",'Paste old sheet'!$A$1:$BZ$1,0),""))</f>
-        <v/>
-      </c>
-      <c r="AC5" s="11">
-        <f>IF(AC3="","",IFERROR(MATCH(AC3&amp;"*",'Paste old sheet'!$A$1:$BZ$1,0),""))</f>
-        <v/>
-      </c>
-      <c r="AD5" s="9" t="n"/>
+      <c r="AB5" s="9" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="12">
@@ -1445,16 +1405,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA6" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB6" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC6" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA6" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -1547,16 +1499,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA7" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB7" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC7" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA7" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -1649,16 +1593,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA8" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB8" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC8" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA8" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -1751,16 +1687,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA9" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB9" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC9" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA9" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -1853,16 +1781,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA10" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB10" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC10" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA10" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -1955,16 +1875,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA11" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB11" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC11" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA11" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2057,16 +1969,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA12" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB12" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC12" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA12" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2159,16 +2063,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA13" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB13" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC13" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA13" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2261,16 +2157,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA14" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB14" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC14" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA14" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2363,16 +2251,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA15" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB15" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC15" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA15" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2465,16 +2345,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA16" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB16" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC16" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA16" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2567,16 +2439,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA17" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB17" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC17" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA17" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2669,16 +2533,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA18" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB18" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC18" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA18" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2771,16 +2627,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA19" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB19" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC19" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA19" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2873,16 +2721,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA20" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB20" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC20" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA20" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -2975,16 +2815,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA21" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB21" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC21" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA21" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3077,16 +2909,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA22" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB22" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC22" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA22" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3179,16 +3003,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA23" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB23" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC23" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA23" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3281,16 +3097,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA24" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB24" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC24" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA24" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3383,16 +3191,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA25" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB25" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC25" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA25" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3485,16 +3285,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA26" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB26" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC26" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA26" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3587,16 +3379,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA27" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB27" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC27" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA27" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3689,16 +3473,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA28" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB28" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC28" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA28" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3791,16 +3567,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA29" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB29" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC29" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA29" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3893,16 +3661,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA30" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB30" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC30" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA30" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -3995,16 +3755,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA31" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB31" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC31" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA31" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -4097,16 +3849,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA32" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB32" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC32" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA32" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -4199,16 +3943,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA33" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB33" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC33" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA33" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -4301,16 +4037,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA34" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB34" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC34" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA34" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -4403,16 +4131,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA35" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB35" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC35" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA35" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -4505,16 +4225,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA36" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB36" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC36" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA36" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -4607,16 +4319,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA37" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB37" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC37" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA37" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -4709,16 +4413,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA38" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB38" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC38" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA38" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -4811,16 +4507,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA39" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB39" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC39" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA39" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -4913,16 +4601,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA40" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB40" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC40" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA40" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5015,16 +4695,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA41" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB41" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC41" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA41" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5117,16 +4789,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA42" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB42" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC42" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA42" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5219,16 +4883,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA43" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB43" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC43" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA43" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5321,16 +4977,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA44" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB44" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC44" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA44" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5423,16 +5071,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA45" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB45" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC45" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA45" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5525,16 +5165,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA46" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB46" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC46" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA46" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5627,16 +5259,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA47" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB47" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC47" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA47" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5729,16 +5353,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA48" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB48" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC48" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA48" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5831,16 +5447,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA49" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB49" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC49" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA49" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -5933,16 +5541,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA50" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB50" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC50" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA50" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6035,16 +5635,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA51" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB51" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC51" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA51" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6137,16 +5729,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA52" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB52" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC52" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA52" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6239,16 +5823,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA53" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB53" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC53" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA53" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6341,16 +5917,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA54" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB54" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC54" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA54" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6443,16 +6011,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA55" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB55" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC55" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA55" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6545,16 +6105,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA56" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB56" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC56" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA56" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6647,16 +6199,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA57" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB57" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC57" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA57" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6749,16 +6293,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA58" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB58" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC58" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA58" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6851,16 +6387,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA59" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB59" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC59" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA59" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -6953,16 +6481,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA60" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB60" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC60" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA60" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7055,16 +6575,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA61" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB61" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC61" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA61" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7157,16 +6669,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA62" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB62" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC62" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA62" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7259,16 +6763,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA63" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB63" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC63" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA63" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7361,16 +6857,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA64" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB64" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC64" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA64" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7463,16 +6951,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA65" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB65" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC65" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA65" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7565,16 +7045,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA66" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB66" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC66" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA66" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7667,16 +7139,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA67" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB67" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC67" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA67" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7769,16 +7233,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA68" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB68" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC68" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA68" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7871,16 +7327,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA69" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB69" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC69" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA69" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -7973,16 +7421,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA70" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB70" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC70" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA70" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8075,16 +7515,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA71" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB71" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC71" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA71" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8177,16 +7609,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA72" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB72" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC72" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA72" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8279,16 +7703,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA73" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB73" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC73" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA73" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8381,16 +7797,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA74" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB74" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC74" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA74" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8483,16 +7891,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA75" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB75" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC75" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA75" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8585,16 +7985,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA76" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB76" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC76" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA76" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8687,16 +8079,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA77" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB77" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC77" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA77" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8789,16 +8173,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA78" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB78" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC78" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA78" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8891,16 +8267,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA79" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB79" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC79" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA79" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -8993,16 +8361,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA80" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB80" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC80" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA80" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -9095,16 +8455,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA81" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB81" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC81" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA81" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -9197,16 +8549,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA82" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB82" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC82" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA82" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -9299,16 +8643,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA83" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB83" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC83" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA83" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -9401,16 +8737,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA84" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB84" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC84" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA84" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -9503,16 +8831,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA85" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB85" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC85" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA85" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -9605,16 +8925,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA86" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB86" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC86" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA86" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -9707,16 +9019,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA87" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB87" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC87" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA87" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -9809,16 +9113,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA88" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB88" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC88" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA88" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -9911,16 +9207,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA89" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB89" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC89" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA89" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10013,16 +9301,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA90" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB90" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC90" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA90" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10115,16 +9395,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA91" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB91" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC91" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA91" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10217,16 +9489,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA92" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB92" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC92" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA92" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10319,16 +9583,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA93" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB93" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC93" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA93" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10421,16 +9677,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA94" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB94" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC94" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA94" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10523,16 +9771,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA95" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB95" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC95" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA95" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10625,16 +9865,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA96" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB96" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC96" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA96" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10727,16 +9959,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA97" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB97" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC97" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA97" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10829,16 +10053,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA98" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB98" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC98" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA98" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -10931,16 +10147,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA99" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB99" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC99" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA99" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11033,16 +10241,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA100" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB100" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC100" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA100" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11135,16 +10335,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA101" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB101" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC101" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA101" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11237,16 +10429,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA102" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB102" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC102" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA102" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11339,16 +10523,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA103" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB103" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC103" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA103" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11441,16 +10617,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA104" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB104" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC104" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA104" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11543,16 +10711,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA105" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB105" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC105" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA105" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11645,16 +10805,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA106" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB106" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC106" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA106" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11747,16 +10899,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA107" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB107" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC107" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA107" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11849,16 +10993,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA108" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB108" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC108" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA108" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -11951,16 +11087,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA109" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB109" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC109" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA109" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12053,16 +11181,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA110" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB110" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC110" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA110" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12155,16 +11275,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA111" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB111" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC111" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA111" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12257,16 +11369,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA112" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB112" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC112" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA112" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12359,16 +11463,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA113" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB113" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC113" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA113" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12461,16 +11557,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA114" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB114" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC114" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA114" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12563,16 +11651,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA115" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB115" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC115" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA115" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12665,16 +11745,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA116" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB116" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC116" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA116" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12767,16 +11839,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA117" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB117" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC117" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA117" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12869,16 +11933,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA118" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB118" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC118" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA118" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -12971,16 +12027,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA119" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB119" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC119" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA119" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13073,16 +12121,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA120" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB120" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC120" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA120" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13175,16 +12215,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA121" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB121" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC121" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA121" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13277,16 +12309,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA122" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB122" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC122" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA122" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13379,16 +12403,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA123" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB123" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC123" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA123" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13481,16 +12497,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA124" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB124" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC124" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA124" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13583,16 +12591,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA125" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB125" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC125" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA125" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13685,16 +12685,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA126" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB126" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC126" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA126" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13787,16 +12779,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA127" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB127" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC127" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA127" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13889,16 +12873,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA128" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB128" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC128" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA128" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -13991,16 +12967,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA129" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB129" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC129" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA129" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -14093,16 +13061,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA130" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB130" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC130" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA130" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -14195,16 +13155,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA131" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB131" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC131" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA131" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -14297,16 +13249,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA132" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB132" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC132" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA132" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -14399,16 +13343,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA133" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB133" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC133" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA133" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -14501,16 +13437,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA134" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB134" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC134" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA134" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -14603,16 +13531,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA135" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB135" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC135" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA135" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -14705,16 +13625,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA136" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB136" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC136" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA136" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -14807,16 +13719,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA137" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB137" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC137" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA137" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -14909,16 +13813,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA138" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB138" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC138" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA138" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15011,16 +13907,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA139" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB139" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC139" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA139" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15113,16 +14001,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA140" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB140" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC140" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA140" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15215,16 +14095,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA141" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB141" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC141" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA141" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15317,16 +14189,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA142" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB142" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC142" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA142" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15419,16 +14283,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA143" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB143" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC143" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA143" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15521,16 +14377,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA144" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB144" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC144" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA144" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15623,16 +14471,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA145" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB145" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC145" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA145" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15725,16 +14565,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA146" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB146" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC146" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA146" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15827,16 +14659,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA147" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB147" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC147" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA147" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -15929,16 +14753,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA148" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB148" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC148" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA148" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16031,16 +14847,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA149" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB149" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC149" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA149" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16133,16 +14941,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA150" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB150" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC150" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA150" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16235,16 +15035,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA151" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB151" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC151" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA151" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16337,16 +15129,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA152" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB152" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC152" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA152" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16439,16 +15223,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA153" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB153" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC153" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA153" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16541,16 +15317,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA154" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB154" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC154" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA154" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16643,16 +15411,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA155" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB155" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC155" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA155" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16745,16 +15505,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA156" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB156" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC156" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA156" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16847,16 +15599,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA157" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB157" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC157" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA157" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -16949,16 +15693,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA158" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB158" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC158" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA158" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17051,16 +15787,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA159" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB159" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC159" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA159" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17153,16 +15881,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA160" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB160" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC160" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA160" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17255,16 +15975,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA161" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB161" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC161" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA161" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17357,16 +16069,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA162" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB162" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC162" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA162" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17459,16 +16163,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA163" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB163" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC163" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA163" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17561,16 +16257,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA164" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB164" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC164" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA164" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17663,16 +16351,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA165" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB165" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC165" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA165" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17765,16 +16445,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA166" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB166" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC166" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA166" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17867,16 +16539,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA167" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB167" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC167" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA167" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -17969,16 +16633,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA168" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB168" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC168" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA168" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18071,16 +16727,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA169" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB169" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC169" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA169" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18173,16 +16821,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA170" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB170" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC170" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA170" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18275,16 +16915,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA171" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB171" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC171" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA171" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18377,16 +17009,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA172" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB172" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC172" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA172" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18479,16 +17103,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA173" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB173" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC173" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA173" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18581,16 +17197,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA174" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB174" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC174" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA174" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18683,16 +17291,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA175" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB175" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC175" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA175" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18785,16 +17385,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA176" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB176" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC176" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA176" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18887,16 +17479,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA177" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB177" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC177" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA177" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -18989,16 +17573,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA178" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB178" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC178" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA178" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -19091,16 +17667,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA179" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB179" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC179" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA179" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -19193,16 +17761,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA180" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB180" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC180" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA180" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -19295,16 +17855,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA181" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB181" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC181" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA181" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -19397,16 +17949,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA182" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB182" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC182" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA182" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -19499,16 +18043,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA183" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB183" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC183" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA183" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -19601,16 +18137,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA184" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB184" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC184" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA184" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -19703,16 +18231,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA185" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB185" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC185" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA185" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -19805,16 +18325,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA186" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB186" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC186" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA186" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -19907,16 +18419,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA187" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB187" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC187" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA187" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20009,16 +18513,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA188" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB188" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC188" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA188" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20111,16 +18607,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA189" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB189" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC189" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA189" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20213,16 +18701,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA190" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB190" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC190" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA190" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20315,16 +18795,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA191" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB191" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC191" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA191" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20417,16 +18889,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA192" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB192" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC192" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA192" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20519,16 +18983,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA193" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB193" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC193" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA193" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20621,16 +19077,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA194" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB194" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC194" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA194" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20723,16 +19171,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA195" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB195" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC195" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA195" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20825,16 +19265,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA196" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB196" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC196" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA196" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -20927,16 +19359,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA197" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB197" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC197" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA197" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21029,16 +19453,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA198" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB198" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC198" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA198" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21131,16 +19547,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA199" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB199" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC199" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA199" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21233,16 +19641,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA200" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB200" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC200" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA200" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21335,16 +19735,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA201" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB201" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC201" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA201" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21437,16 +19829,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA202" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB202" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC202" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA202" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21539,16 +19923,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA203" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB203" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC203" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA203" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21641,16 +20017,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA204" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB204" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC204" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA204" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21743,16 +20111,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA205" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB205" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC205" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA205" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21845,16 +20205,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA206" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB206" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC206" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA206" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -21947,16 +20299,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA207" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB207" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC207" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA207" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22049,16 +20393,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA208" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB208" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC208" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA208" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22151,16 +20487,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA209" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB209" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC209" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA209" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22253,16 +20581,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA210" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB210" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC210" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA210" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22355,16 +20675,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA211" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB211" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC211" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA211" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22457,16 +20769,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA212" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB212" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC212" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA212" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22559,16 +20863,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA213" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB213" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC213" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA213" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22661,16 +20957,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA214" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB214" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC214" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA214" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22763,16 +21051,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA215" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB215" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC215" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA215" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22865,16 +21145,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA216" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB216" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC216" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA216" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -22967,16 +21239,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA217" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB217" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC217" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA217" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23069,16 +21333,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA218" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB218" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC218" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA218" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23171,16 +21427,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA219" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB219" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC219" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA219" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23273,16 +21521,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA220" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB220" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC220" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA220" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23375,16 +21615,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA221" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB221" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC221" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA221" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23477,16 +21709,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA222" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB222" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC222" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA222" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23579,16 +21803,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA223" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB223" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC223" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA223" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23681,16 +21897,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA224" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB224" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC224" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA224" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23783,16 +21991,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA225" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB225" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC225" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA225" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23885,16 +22085,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA226" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB226" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC226" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA226" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -23987,16 +22179,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA227" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB227" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC227" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA227" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -24089,16 +22273,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA228" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB228" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC228" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA228" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -24191,16 +22367,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA229" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB229" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC229" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA229" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -24293,16 +22461,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA230" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB230" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC230" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA230" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -24395,16 +22555,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA231" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB231" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC231" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA231" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -24497,16 +22649,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA232" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB232" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC232" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA232" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -24599,16 +22743,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA233" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB233" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC233" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA233" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -24701,16 +22837,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA234" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB234" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC234" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA234" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -24803,16 +22931,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA235" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB235" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC235" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA235" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -24905,16 +23025,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA236" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB236" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC236" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA236" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25007,16 +23119,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA237" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB237" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC237" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA237" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25109,16 +23213,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA238" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB238" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC238" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA238" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25211,16 +23307,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA239" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB239" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC239" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA239" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25313,16 +23401,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA240" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB240" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC240" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA240" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25415,16 +23495,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA241" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB241" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC241" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA241" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25517,16 +23589,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA242" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB242" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC242" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA242" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25619,16 +23683,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA243" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB243" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC243" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA243" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25721,16 +23777,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA244" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB244" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC244" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA244" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25823,16 +23871,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA245" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB245" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC245" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA245" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -25925,16 +23965,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA246" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB246" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC246" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA246" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26027,16 +24059,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA247" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB247" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC247" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA247" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26129,16 +24153,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA248" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB248" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC248" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA248" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26231,16 +24247,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA249" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB249" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC249" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA249" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26333,16 +24341,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA250" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB250" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC250" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA250" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26435,16 +24435,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA251" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB251" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC251" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA251" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26537,16 +24529,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA252" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB252" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC252" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA252" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26639,16 +24623,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA253" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB253" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC253" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA253" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26741,16 +24717,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA254" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB254" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC254" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA254" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26843,16 +24811,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA255" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB255" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC255" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA255" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -26945,16 +24905,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA256" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB256" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC256" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA256" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27047,16 +24999,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA257" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB257" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC257" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA257" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27149,16 +25093,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA258" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB258" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC258" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA258" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27251,16 +25187,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA259" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB259" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC259" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA259" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27353,16 +25281,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA260" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB260" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC260" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA260" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27455,16 +25375,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA261" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB261" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC261" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA261" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27557,16 +25469,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA262" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB262" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC262" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA262" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27659,16 +25563,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA263" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB263" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC263" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA263" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27761,16 +25657,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA264" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB264" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC264" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA264" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27863,16 +25751,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA265" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB265" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC265" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA265" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -27965,16 +25845,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA266" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB266" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC266" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA266" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28067,16 +25939,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA267" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB267" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC267" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA267" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28169,16 +26033,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA268" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB268" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC268" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA268" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28271,16 +26127,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA269" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB269" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC269" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA269" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28373,16 +26221,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA270" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB270" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC270" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA270" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28475,16 +26315,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA271" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB271" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC271" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA271" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28577,16 +26409,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA272" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB272" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC272" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA272" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28679,16 +26503,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA273" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB273" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC273" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA273" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28781,16 +26597,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA274" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB274" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC274" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA274" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28883,16 +26691,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA275" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB275" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC275" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA275" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -28985,16 +26785,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA276" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB276" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC276" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA276" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -29087,16 +26879,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA277" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB277" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC277" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA277" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -29189,16 +26973,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA278" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB278" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC278" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA278" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -29291,16 +27067,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA279" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB279" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC279" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA279" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -29393,16 +27161,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA280" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB280" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC280" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA280" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -29495,16 +27255,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA281" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB281" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC281" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA281" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -29597,16 +27349,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA282" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB282" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC282" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA282" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -29699,16 +27443,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA283" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB283" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC283" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA283" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -29801,16 +27537,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA284" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB284" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC284" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA284" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -29903,16 +27631,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA285" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB285" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC285" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA285" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30005,16 +27725,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA286" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB286" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC286" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA286" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30107,16 +27819,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA287" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB287" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC287" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA287" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30209,16 +27913,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA288" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB288" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC288" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA288" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30311,16 +28007,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA289" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB289" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC289" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA289" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30413,16 +28101,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA290" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB290" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC290" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA290" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30515,16 +28195,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA291" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB291" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC291" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA291" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30617,16 +28289,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA292" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB292" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC292" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA292" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30719,16 +28383,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA293" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB293" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC293" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA293" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30821,16 +28477,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA294" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB294" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC294" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA294" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -30923,16 +28571,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA295" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB295" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC295" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA295" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31025,16 +28665,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA296" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB296" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC296" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA296" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31127,16 +28759,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA297" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB297" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC297" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA297" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31229,16 +28853,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA298" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB298" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC298" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA298" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31331,16 +28947,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA299" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB299" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC299" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA299" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31433,16 +29041,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA300" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB300" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC300" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA300" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31535,16 +29135,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA301" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB301" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC301" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA301" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31637,16 +29229,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA302" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB302" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC302" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA302" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31739,16 +29323,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA303" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB303" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC303" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA303" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31841,16 +29417,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA304" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB304" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC304" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA304" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -31943,16 +29511,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA305" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB305" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC305" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA305" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32045,16 +29605,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA306" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB306" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC306" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA306" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32147,16 +29699,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA307" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB307" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC307" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA307" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32249,16 +29793,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA308" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB308" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC308" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA308" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32351,16 +29887,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA309" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB309" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC309" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA309" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32453,16 +29981,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA310" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB310" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC310" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA310" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32555,16 +30075,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA311" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB311" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC311" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA311" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32657,16 +30169,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA312" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB312" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC312" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA312" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32759,16 +30263,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA313" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB313" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC313" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA313" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32861,16 +30357,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA314" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB314" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC314" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA314" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -32963,16 +30451,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA315" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB315" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC315" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA315" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33065,16 +30545,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA316" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB316" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC316" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA316" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33167,16 +30639,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA317" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB317" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC317" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA317" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33269,16 +30733,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA318" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB318" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC318" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA318" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33371,16 +30827,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA319" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB319" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC319" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA319" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33473,16 +30921,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA320" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB320" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC320" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA320" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33575,16 +31015,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA321" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB321" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC321" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA321" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33677,16 +31109,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA322" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB322" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC322" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA322" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33779,16 +31203,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA323" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB323" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC323" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA323" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33881,16 +31297,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA324" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB324" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC324" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA324" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -33983,16 +31391,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA325" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB325" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC325" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA325" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -34085,16 +31485,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA326" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB326" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC326" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA326" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -34187,16 +31579,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA327" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB327" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC327" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA327" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -34289,16 +31673,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA328" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB328" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC328" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA328" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -34391,16 +31767,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA329" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB329" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC329" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA329" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -34493,16 +31861,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA330" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB330" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC330" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA330" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -34595,16 +31955,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA331" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB331" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC331" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA331" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -34697,16 +32049,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA332" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB332" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC332" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA332" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -34799,16 +32143,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA333" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB333" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC333" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA333" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -34901,16 +32237,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA334" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB334" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC334" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA334" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35003,16 +32331,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA335" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB335" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC335" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA335" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35105,16 +32425,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA336" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB336" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC336" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA336" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35207,16 +32519,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA337" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB337" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC337" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA337" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35309,16 +32613,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA338" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB338" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC338" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA338" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35411,16 +32707,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA339" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB339" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC339" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA339" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35513,16 +32801,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA340" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB340" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC340" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA340" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35615,16 +32895,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA341" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB341" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC341" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA341" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35717,16 +32989,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA342" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB342" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC342" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA342" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35819,16 +33083,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA343" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB343" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC343" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA343" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -35921,16 +33177,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA344" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB344" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC344" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA344" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36023,16 +33271,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA345" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB345" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC345" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA345" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36125,16 +33365,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA346" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB346" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC346" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA346" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36227,16 +33459,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA347" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB347" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC347" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA347" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36329,16 +33553,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA348" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB348" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC348" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA348" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36431,16 +33647,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA349" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB349" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC349" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA349" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36533,16 +33741,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA350" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB350" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC350" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA350" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36635,16 +33835,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA351" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB351" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC351" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA351" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36737,16 +33929,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA352" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB352" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC352" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA352" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36839,16 +34023,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA353" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB353" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC353" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA353" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -36941,16 +34117,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA354" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB354" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC354" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA354" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37043,16 +34211,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA355" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB355" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC355" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA355" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37145,16 +34305,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA356" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB356" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC356" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA356" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37247,16 +34399,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA357" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB357" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC357" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA357" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37349,16 +34493,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA358" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB358" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC358" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA358" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37451,16 +34587,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA359" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB359" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC359" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA359" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37553,16 +34681,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA360" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB360" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC360" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA360" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37655,16 +34775,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA361" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB361" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC361" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA361" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37757,16 +34869,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA362" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB362" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC362" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA362" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37859,16 +34963,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA363" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB363" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC363" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA363" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -37961,16 +35057,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA364" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB364" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC364" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA364" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38063,16 +35151,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA365" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB365" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC365" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA365" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38165,16 +35245,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA366" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB366" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC366" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA366" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38267,16 +35339,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA367" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB367" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC367" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA367" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38369,16 +35433,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA368" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB368" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC368" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA368" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38471,16 +35527,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA369" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB369" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC369" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA369" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38573,16 +35621,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA370" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB370" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC370" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA370" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38675,16 +35715,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA371" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB371" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC371" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA371" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38777,16 +35809,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA372" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB372" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC372" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA372" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38879,16 +35903,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA373" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB373" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC373" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA373" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -38981,16 +35997,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA374" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB374" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC374" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA374" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -39083,16 +36091,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA375" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB375" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC375" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA375" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -39185,16 +36185,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA376" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB376" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC376" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA376" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -39287,16 +36279,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA377" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB377" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC377" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA377" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -39389,16 +36373,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA378" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB378" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC378" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA378" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -39491,16 +36467,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA379" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB379" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC379" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA379" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -39593,16 +36561,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA380" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB380" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC380" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA380" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -39695,16 +36655,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA381" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB381" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC381" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA381" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -39797,16 +36749,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA382" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB382" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC382" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA382" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -39899,16 +36843,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA383" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB383" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC383" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA383" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40001,16 +36937,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA384" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB384" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC384" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA384" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40103,16 +37031,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA385" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB385" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC385" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA385" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40205,16 +37125,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA386" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB386" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC386" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA386" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40307,16 +37219,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA387" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB387" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC387" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA387" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40409,16 +37313,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA388" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB388" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC388" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA388" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40511,16 +37407,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA389" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB389" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC389" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA389" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40613,16 +37501,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA390" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB390" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC390" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA390" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40715,16 +37595,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA391" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB391" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC391" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA391" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40817,16 +37689,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA392" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB392" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC392" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA392" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -40919,16 +37783,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA393" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB393" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC393" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA393" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41021,16 +37877,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA394" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB394" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC394" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA394" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41123,16 +37971,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA395" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB395" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC395" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA395" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41225,16 +38065,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA396" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB396" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC396" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA396" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41327,16 +38159,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA397" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB397" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC397" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA397" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41429,16 +38253,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA398" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB398" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC398" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA398" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41531,16 +38347,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA399" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB399" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC399" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA399" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41633,16 +38441,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA400" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB400" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC400" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA400" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41735,16 +38535,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA401" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB401" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC401" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA401" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41837,16 +38629,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA402" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB402" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC402" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA402" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -41939,16 +38723,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA403" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB403" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC403" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA403" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -42041,16 +38817,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA404" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB404" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC404" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA404" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -42143,16 +38911,8 @@
         <f>IF(ISNUMBER(Z$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,Z$5)),"")</f>
         <v/>
       </c>
-      <c r="AA405" s="13">
-        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AB405" s="12">
-        <f>IF(ISNUMBER(AB$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AB$5)),"")</f>
-        <v/>
-      </c>
-      <c r="AC405" s="12">
-        <f>IF(ISNUMBER(AC$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AC$5)),"")</f>
+      <c r="AA405" s="12">
+        <f>IF(ISNUMBER(AA$5),IF(INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)="","",INDEX('Paste old sheet'!$A$2:$BZ$401,ROW()-5,AA$5)),"")</f>
         <v/>
       </c>
     </row>
@@ -42232,13 +38992,8 @@
       <formula>AND(ISTEXT(Y6),Y6&lt;&gt;"",Y6&lt;&gt;"DNA",Y6&lt;&gt;"N/A")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AA6:AA405">
-    <cfRule type="expression" priority="16" dxfId="0">
-      <formula>AND(ISTEXT(AA6),AA6&lt;&gt;"",AA6&lt;&gt;"DNA",AA6&lt;&gt;"N/A")</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A4:AD4">
-    <cfRule type="expression" priority="17" dxfId="1">
+  <conditionalFormatting sqref="A4:AB4">
+    <cfRule type="expression" priority="16" dxfId="1">
       <formula>A4="NOT FOUND"</formula>
     </cfRule>
   </conditionalFormatting>
